--- a/5/search/FY5_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY5_Missile1_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131</v>
+        <v>94.8</v>
       </c>
       <c r="C3" t="n">
-        <v>126.3</v>
+        <v>99.8</v>
       </c>
       <c r="D3" t="n">
-        <v>15.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="F3" t="n">
-        <v>3.600000000000001</v>
+        <v>3.800000000000001</v>
       </c>
     </row>
   </sheetData>
